--- a/markets/prospects/Kuwait_Ecommerce_Prospects.xlsx
+++ b/markets/prospects/Kuwait_Ecommerce_Prospects.xlsx
@@ -519,12 +519,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Company Phone Numbers (comma separated)</t>
+          <t>Company Phone Numbers</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Company Emails (comma separated; marketing/sales/business only)</t>
+          <t>Company Emails</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">

--- a/markets/prospects/Kuwait_Ecommerce_Prospects.xlsx
+++ b/markets/prospects/Kuwait_Ecommerce_Prospects.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Master Prospects'!$A$1:$J$183</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decision Makers'!$A$1:$G$231</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decision Makers'!$A$1:$G$319</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4314,12 +4314,12 @@
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Sulaiman Al Wahyan</t>
         </is>
       </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Founder, Pinoy Hyper Kuwait</t>
         </is>
       </c>
     </row>
@@ -4656,12 +4656,12 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Zahraa Alqallaf</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Partner &amp; Owner-Operator</t>
         </is>
       </c>
     </row>
@@ -4802,12 +4802,12 @@
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Shaimaa Samir</t>
         </is>
       </c>
       <c r="J89" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Marketing Manager (Pharmalife group)</t>
         </is>
       </c>
     </row>
@@ -4850,12 +4850,12 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mohammed AlKassas</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>General Manager Watches &amp; Jewelry, Behbehani Watch World</t>
         </is>
       </c>
     </row>
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Shashank Shobhit</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Head of Ecommerce, Damas Jewellery</t>
         </is>
       </c>
     </row>
@@ -4987,19 +4987,19 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="H93" s="5" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/district91</t>
         </is>
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hazem Hasna</t>
         </is>
       </c>
       <c r="J93" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>General Manager, District General Trading &amp; Contracting Co. (My Colors)</t>
         </is>
       </c>
     </row>
@@ -5035,19 +5035,19 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/district91</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hazem Hasna</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>General Manager, District General Trading &amp; Contracting Co. (My Colors)</t>
         </is>
       </c>
     </row>
@@ -5238,12 +5238,12 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Abdulwahab Alessa</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>General Manager, MF Food</t>
         </is>
       </c>
     </row>
@@ -5334,12 +5334,12 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Nikhil Kosuri</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Director of Digital, Ooredoo Kuwait</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>info@waleedtoys.com</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mohamed Aref</t>
         </is>
       </c>
       <c r="J101" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Ecommerce Manager</t>
         </is>
       </c>
     </row>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mohamad Barada</t>
         </is>
       </c>
       <c r="J103" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Marketing E-commerce &amp; Concept Manager, Al Sirhan Shoes</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>+965 51233038</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Asif Juzar</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Founder, Pro Sports Kuwait</t>
         </is>
       </c>
     </row>
@@ -5670,12 +5670,12 @@
       </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Yasser Taher</t>
         </is>
       </c>
       <c r="J107" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Chief Executive Officer, MAGRABi Retail Group</t>
         </is>
       </c>
     </row>
@@ -5718,12 +5718,12 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Nasir Mucedidi</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Founder &amp; CEO</t>
         </is>
       </c>
     </row>
@@ -6006,12 +6006,12 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Lynn Abiad</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>General Manager, Ecommerce - Level Shoes (Chalhoub Group)</t>
         </is>
       </c>
     </row>
@@ -6150,12 +6150,12 @@
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Chirin Khawatmi</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Chief Brand Officer, Mumzworld</t>
         </is>
       </c>
     </row>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mariana Gaspar Rodrigues</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Marketing &amp; F&amp;B Director - Middle East, L'Occitane Group</t>
         </is>
       </c>
     </row>
@@ -6342,12 +6342,12 @@
       </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Amir Al-Hinnawi</t>
         </is>
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Managing Partner, Starco Holding; CEO Bevava (e-commerce)</t>
         </is>
       </c>
     </row>
@@ -6392,12 +6392,12 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Osama Ishak</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Ahmed Ismail</t>
         </is>
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Regional Head of E-Commerce, Jashanmal Group (Clarks GCC e-commerce)</t>
         </is>
       </c>
     </row>
@@ -6488,12 +6488,12 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Jassim Ismaeil Al-Awadhi</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Chief Executive Officer, Al Rajhi Bank Kuwait</t>
         </is>
       </c>
     </row>
@@ -6529,19 +6529,19 @@
           <t>info@mogahwi.com.kw</t>
         </is>
       </c>
-      <c r="H125" s="5" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H125" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mogahwi-stationery</t>
         </is>
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hamad Al-Mogahwi</t>
         </is>
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>General Manager</t>
         </is>
       </c>
     </row>
@@ -6584,12 +6584,12 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mahmoud A.</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Ecommerce &amp; Channels Operations Manager, Falcon Store (New Market Company)</t>
         </is>
       </c>
     </row>
@@ -6625,9 +6625,9 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="H127" s="5" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H127" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/telefonati</t>
         </is>
       </c>
       <c r="I127" s="5" t="inlineStr">
@@ -6673,19 +6673,19 @@
           <t>info@pharmalife-kw.com</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pharmalifekuwait</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Shaimaa Samir</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
     </row>
@@ -6809,12 +6809,12 @@
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>+965 24967770</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>info@samsonite.com.kw</t>
         </is>
       </c>
       <c r="H131" s="6" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Ahmed Ismail</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Regional Head of E-Commerce, Jashanmal Group</t>
         </is>
       </c>
     </row>
@@ -6920,12 +6920,12 @@
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Muffaddal Kalla</t>
         </is>
       </c>
       <c r="J133" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>CEO</t>
         </is>
       </c>
     </row>
@@ -7064,12 +7064,12 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Saleem Awad</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Co-founder &amp; Managing Director</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>mahmoudanwar@twentyfive.com.kw</t>
         </is>
       </c>
       <c r="H139" s="6" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>+965 22286224, +965 50351841</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mariam Mohammad</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Marketing and Public Relations Manager, LUSH Kuwait</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>online@orp.com.kw</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
@@ -7356,12 +7356,12 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Yousef Alnemah</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Founder &amp; CEO, Off Road Performance (ORP)</t>
         </is>
       </c>
     </row>
@@ -7500,12 +7500,12 @@
       </c>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Anas Ismail</t>
         </is>
       </c>
       <c r="J145" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Head of E-commerce &amp; Performance, Junaid Perfumes</t>
         </is>
       </c>
     </row>
@@ -7548,12 +7548,12 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Jean Thomas</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Chief Marketing, Tech &amp; Product Officer (CMO &amp; CPTO), Eyewa</t>
         </is>
       </c>
     </row>
@@ -7836,12 +7836,12 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Syed Adil Adnan</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>E-Commerce &amp; Digital Media Manager / Head of E-Commerce, Swiss Arabian Perfumes Group (group-level)</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>admin@gamestore.com.kw</t>
         </is>
       </c>
       <c r="H153" s="5" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Falah Al-Ajmi</t>
         </is>
       </c>
       <c r="J153" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Owner, Co-founder &amp; CEO, Game Store</t>
         </is>
       </c>
     </row>
@@ -8078,12 +8078,12 @@
       </c>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mohammed Sheikh Ibrahim (محمد شيخ ابراهيم)</t>
         </is>
       </c>
       <c r="J157" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Marketing Manager, eMarket Kuwait</t>
         </is>
       </c>
     </row>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>ecommerce@skindollize.com</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
@@ -8222,12 +8222,12 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Bodour Alhajji</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>CEO &amp; Founder, Skindollize (The Face Shop Kuwait)</t>
         </is>
       </c>
     </row>
@@ -8270,12 +8270,12 @@
       </c>
       <c r="I161" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Micheline Berzy</t>
         </is>
       </c>
       <c r="J161" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Head of Marketing - Fashion Brands (incl. Ted Baker), Al-Futtaim</t>
         </is>
       </c>
     </row>
@@ -8366,12 +8366,12 @@
       </c>
       <c r="I163" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Fatima AlQattan</t>
         </is>
       </c>
       <c r="J163" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Owner / Founder, Sniggles Kuwait</t>
         </is>
       </c>
     </row>
@@ -8462,12 +8462,12 @@
       </c>
       <c r="I165" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Shemil Ay</t>
         </is>
       </c>
       <c r="J165" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>General Manager &amp; Executive Director</t>
         </is>
       </c>
     </row>
@@ -8558,12 +8558,12 @@
       </c>
       <c r="I167" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Sarah N. AlThekair</t>
         </is>
       </c>
       <c r="J167" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Co-Founder &amp; CEO</t>
         </is>
       </c>
     </row>
@@ -8644,22 +8644,22 @@
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="H169" s="5" t="inlineStr">
-        <is>
-          <t>Not found</t>
+          <t>info@stylati.fashion</t>
+        </is>
+      </c>
+      <c r="H169" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/stylati</t>
         </is>
       </c>
       <c r="I169" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mohammed Barakat</t>
         </is>
       </c>
       <c r="J169" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Co-Founder &amp; CEO</t>
         </is>
       </c>
     </row>
@@ -8743,19 +8743,19 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="H171" s="5" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H171" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/jomla-ae</t>
         </is>
       </c>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mohammed Al Zoubi</t>
         </is>
       </c>
       <c r="J171" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Co-Founder, E-Commerce &amp; Digital Marketing Manager</t>
         </is>
       </c>
     </row>
@@ -8798,12 +8798,12 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hamed Zaghloul</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Marketing Manager, Hilti Kuwait</t>
         </is>
       </c>
     </row>
@@ -8990,12 +8990,12 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Rania Mahmoud</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Marketing Manager Kuwait, NAOS</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Ali Al-Yousifi</t>
         </is>
       </c>
       <c r="J177" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Owner / Co-founder</t>
         </is>
       </c>
     </row>
@@ -9086,12 +9086,12 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Abdulaziz Alrefaie</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Chief Executive Officer, Aldur Almanthoor</t>
         </is>
       </c>
     </row>
@@ -9119,7 +9119,7 @@
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>+965 55041174</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>info@gamesq8.com</t>
         </is>
       </c>
       <c r="H180" s="3" t="inlineStr">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Ammar Jassim Hussain Ashkanani</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Company Manager</t>
         </is>
       </c>
     </row>
@@ -9510,150 +9510,157 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B92" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId171"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B96" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B108" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B121" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B122" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B123" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B124" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B126" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B127" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B128" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B129" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B130" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B131" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B132" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B133" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B134" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B135" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B136" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B137" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B138" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B139" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B140" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B141" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B142" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B143" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B144" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B145" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B146" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B147" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B148" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B149" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B150" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B151" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B152" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B153" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B154" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B155" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B156" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B157" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B158" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B159" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B160" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B161" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B162" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B163" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B164" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B165" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B166" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B167" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B168" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B169" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B170" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B171" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B172" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B173" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B174" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B175" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B176" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B177" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B178" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B179" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B180" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B181" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B182" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B183" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B96" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B108" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B121" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B122" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B123" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B124" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B126" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B127" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B128" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B129" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B130" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B131" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B132" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B133" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B134" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B135" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B136" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B137" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B138" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B139" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B140" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B141" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B142" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B143" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B144" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B145" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B146" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B147" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B148" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B149" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B150" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B151" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B152" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B153" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B154" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B155" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B156" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B157" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B158" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B159" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B160" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B161" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B162" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B163" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B164" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B165" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B166" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B167" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B168" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B169" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B170" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B171" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B172" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B173" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B174" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B175" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B176" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B177" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B178" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B179" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B180" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B181" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B182" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B183" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId323"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9666,7 +9673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G231"/>
+  <dimension ref="A1:G319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -16489,22 +16496,22 @@
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
         <is>
-          <t>Massimo Dutti Kuwait (Alshaya)</t>
+          <t>Pinoy Hyper Kuwait</t>
         </is>
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>https://www.massimodutti.com/kw/</t>
+          <t>https://pinoyhyper.com/</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>Khuzema Saifuddin</t>
+          <t>Sulaiman Al Wahyan</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>eCommerce Lead, Alshaya Group (Kuwait)</t>
+          <t>Founder, Pinoy Hyper Kuwait</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
@@ -16517,9 +16524,9 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G185" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/khuzema-saifuddin-534922a6</t>
+      <c r="G185" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
@@ -16536,12 +16543,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Rob Silsbury</t>
+          <t>Khuzema Saifuddin</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Vice President Ecommerce, Alshaya Group (all brand websites/apps across MENA)</t>
+          <t>eCommerce Lead, Alshaya Group (Kuwait)</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -16556,7 +16563,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/robsilsbury</t>
+          <t>https://www.linkedin.com/in/khuzema-saifuddin-534922a6</t>
         </is>
       </c>
     </row>
@@ -16573,12 +16580,12 @@
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>Maëlle Mandjee (Basselot)</t>
+          <t>Rob Silsbury</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>Director of Ecommerce, Alshaya Group</t>
+          <t>Vice President Ecommerce, Alshaya Group (all brand websites/apps across MENA)</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
@@ -16593,29 +16600,29 @@
       </c>
       <c r="G187" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ma%C3%ABlle-basselot</t>
+          <t>https://www.linkedin.com/in/robsilsbury</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Ajmal Perfumes</t>
+          <t>Massimo Dutti Kuwait (Alshaya)</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>https://en-kwt.ajmal.com/</t>
+          <t>https://www.massimodutti.com/kw/</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Mohammad Tausif Salah</t>
+          <t>Maëlle Mandjee (Basselot)</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Head of Ecommerce, Ajmal Perfumes</t>
+          <t>Director of Ecommerce, Alshaya Group</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -16630,29 +16637,29 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/tausif-salah</t>
+          <t>https://www.linkedin.com/in/ma%C3%ABlle-basselot</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>SNKR Kuwait (AAW)</t>
+          <t>Ajmal Perfumes</t>
         </is>
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>https://www.snkr.com.kw/</t>
+          <t>https://en-kwt.ajmal.com/</t>
         </is>
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>Murtaza Fakhruddin</t>
+          <t>Mohammad Tausif Salah</t>
         </is>
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>Senior Projects Manager - Ecommerce, Ali Abdulwahab Al Mutawa Commercial Co. (AAW) (LinkedIn headline; experience entry still lists Head of Ecommerce since Mar 2020)</t>
+          <t>Head of Ecommerce, Ajmal Perfumes</t>
         </is>
       </c>
       <c r="E189" s="5" t="inlineStr">
@@ -16667,7 +16674,7 @@
       </c>
       <c r="G189" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/murtaza-fakhruddin-0692681b</t>
+          <t>https://linkedin.com/in/tausif-salah</t>
         </is>
       </c>
     </row>
@@ -16684,12 +16691,12 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Hala Thiab</t>
+          <t>Murtaza Fakhruddin</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Senior eCommerce Manager, Ali Abdulwahab Al Mutawa Commercial Co. (AAW: Al Mutawa Pharmacies, JYSK Kuwait)</t>
+          <t>Senior Projects Manager - Ecommerce, Ali Abdulwahab Al Mutawa Commercial Co. (AAW) (LinkedIn headline; experience entry still lists Head of Ecommerce since Mar 2020)</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -16704,7 +16711,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/hala-thiab-44a60956</t>
+          <t>https://www.linkedin.com/in/murtaza-fakhruddin-0692681b</t>
         </is>
       </c>
     </row>
@@ -16721,12 +16728,12 @@
       </c>
       <c r="C191" s="5" t="inlineStr">
         <is>
-          <t>Jamie Aparicio</t>
+          <t>Hala Thiab</t>
         </is>
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>Head of Digital Marketing, Ali Abdulwahab Al Mutawa Commercial Co. (11 brand websites)</t>
+          <t>Senior eCommerce Manager, Ali Abdulwahab Al Mutawa Commercial Co. (AAW: Al Mutawa Pharmacies, JYSK Kuwait)</t>
         </is>
       </c>
       <c r="E191" s="5" t="inlineStr">
@@ -16741,7 +16748,7 @@
       </c>
       <c r="G191" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jamie-aparicio</t>
+          <t>https://www.linkedin.com/in/hala-thiab-44a60956</t>
         </is>
       </c>
     </row>
@@ -16758,12 +16765,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Asmaa Mariee</t>
+          <t>Jamie Aparicio</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>E-Commerce Merchandiser, AAW (Intersport, The Athlete's Foot, SNKR Kuwait sites)</t>
+          <t>Head of Digital Marketing, Ali Abdulwahab Al Mutawa Commercial Co. (11 brand websites)</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -16778,29 +16785,29 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/asmaa-mariee</t>
+          <t>https://www.linkedin.com/in/jamie-aparicio</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t>Charles &amp; Keith</t>
+          <t>SNKR Kuwait (AAW)</t>
         </is>
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>https://www.charleskeith.com/kw/</t>
+          <t>https://www.snkr.com.kw/</t>
         </is>
       </c>
       <c r="C193" s="5" t="inlineStr">
         <is>
-          <t>Plama Spetsova</t>
+          <t>Asmaa Mariee</t>
         </is>
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>General Manager, Digital Commerce &amp; Technology, Apparel Group</t>
+          <t>E-Commerce Merchandiser, AAW (Intersport, The Athlete's Foot, SNKR Kuwait sites)</t>
         </is>
       </c>
       <c r="E193" s="5" t="inlineStr">
@@ -16815,7 +16822,7 @@
       </c>
       <c r="G193" s="6" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/plama-spetsova</t>
+          <t>https://www.linkedin.com/in/asmaa-mariee</t>
         </is>
       </c>
     </row>
@@ -16832,12 +16839,12 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Nisrine Zibara</t>
+          <t>Plama Spetsova</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Regional Brand Marketing Manager - Charles &amp; Keith and Pedro (UAE, KSA, Qatar, Bahrain, Oman &amp; Kuwait), Apparel Group</t>
+          <t>General Manager, Digital Commerce &amp; Technology, Apparel Group</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -16852,29 +16859,29 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/nisrine-zibara-989366120</t>
+          <t>https://linkedin.com/in/plama-spetsova</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
         <is>
-          <t>Dyson Kuwait</t>
+          <t>Charles &amp; Keith</t>
         </is>
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>https://www.dyson.com.kw/</t>
+          <t>https://www.charleskeith.com/kw/</t>
         </is>
       </c>
       <c r="C195" s="5" t="inlineStr">
         <is>
-          <t>Francois Marque</t>
+          <t>Nisrine Zibara</t>
         </is>
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>Head of eCommerce Middle East &amp; Africa, Dyson</t>
+          <t>Regional Brand Marketing Manager - Charles &amp; Keith and Pedro (UAE, KSA, Qatar, Bahrain, Oman &amp; Kuwait), Apparel Group</t>
         </is>
       </c>
       <c r="E195" s="5" t="inlineStr">
@@ -16889,29 +16896,29 @@
       </c>
       <c r="G195" s="6" t="inlineStr">
         <is>
-          <t>https://ae.linkedin.com/in/francois-marque</t>
+          <t>https://linkedin.com/in/nisrine-zibara-989366120</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Dyson Kuwait</t>
+          <t>Amal Al Kuwait</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>https://www.dyson.com.kw/</t>
+          <t>https://amalalkuwait.com/</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Kumar Sambhav Verma</t>
+          <t>Zahraa Alqallaf</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Head - Marketing, Customer Experience &amp; Ecom, Jumbo Group (Dyson distributor)</t>
+          <t>Partner &amp; Owner-Operator, Amal Al-Kuwait</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -16926,29 +16933,29 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/kumarsambhav</t>
+          <t>https://linkedin.com/in/zahraa-alqallaf-2a0805355</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>Pull&amp;Bear Kuwait (Alshaya)</t>
+          <t>Amal Al Kuwait</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>https://www.pullandbear.com/kw/</t>
+          <t>https://amalalkuwait.com/</t>
         </is>
       </c>
       <c r="C197" s="5" t="inlineStr">
         <is>
-          <t>Khuzema Saifuddin</t>
+          <t>Ali AlQallaf</t>
         </is>
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
-          <t>eCommerce Lead, Alshaya Group (Kuwait)</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="E197" s="5" t="inlineStr">
@@ -16963,29 +16970,29 @@
       </c>
       <c r="G197" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/khuzema-saifuddin-534922a6</t>
+          <t>https://linkedin.com/in/ali-alqallaf-8bb7b4130</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Pull&amp;Bear Kuwait (Alshaya)</t>
+          <t>Dyson Kuwait</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>https://www.pullandbear.com/kw/</t>
+          <t>https://www.dyson.com.kw/</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Rob Silsbury</t>
+          <t>Francois Marque</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Vice President Ecommerce, Alshaya Group (all brand websites/apps across MENA)</t>
+          <t>Head of eCommerce Middle East &amp; Africa, Dyson</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -17000,29 +17007,29 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/robsilsbury</t>
+          <t>https://ae.linkedin.com/in/francois-marque</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
         <is>
-          <t>Pull&amp;Bear Kuwait (Alshaya)</t>
+          <t>Dyson Kuwait</t>
         </is>
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>https://www.pullandbear.com/kw/</t>
+          <t>https://www.dyson.com.kw/</t>
         </is>
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>Maëlle Mandjee (Basselot)</t>
+          <t>Kumar Sambhav Verma</t>
         </is>
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
-          <t>Director of Ecommerce, Alshaya Group</t>
+          <t>Head - Marketing, Customer Experience &amp; Ecom, Jumbo Group (Dyson distributor)</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
@@ -17037,29 +17044,29 @@
       </c>
       <c r="G199" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ma%C3%ABlle-basselot</t>
+          <t>https://linkedin.com/in/kumarsambhav</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>Muji</t>
+          <t>Pull&amp;Bear Kuwait (Alshaya)</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>https://www.muji.com.kw/</t>
+          <t>https://www.pullandbear.com/kw/</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Rob Silsbury</t>
+          <t>Khuzema Saifuddin</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Vice President Ecommerce, Alshaya Group (all brand websites/apps across MENA)</t>
+          <t>eCommerce Lead, Alshaya Group (Kuwait)</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -17074,29 +17081,29 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/robsilsbury</t>
+          <t>https://www.linkedin.com/in/khuzema-saifuddin-534922a6</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
         <is>
-          <t>Splash Kuwait (Landmark Group)</t>
+          <t>Pull&amp;Bear Kuwait (Alshaya)</t>
         </is>
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>https://www.splashfashions.com/kw/</t>
+          <t>https://www.pullandbear.com/kw/</t>
         </is>
       </c>
       <c r="C201" s="5" t="inlineStr">
         <is>
-          <t>Reddy Prasad</t>
+          <t>Rob Silsbury</t>
         </is>
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
-          <t>Manager E-Commerce (Associate General Manager E-Commerce), Landmark Group Kuwait</t>
+          <t>Vice President Ecommerce, Alshaya Group (all brand websites/apps across MENA)</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
@@ -17111,29 +17118,29 @@
       </c>
       <c r="G201" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/reddy-prasad-a20b5358</t>
+          <t>https://www.linkedin.com/in/robsilsbury</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>Splash Kuwait (Landmark Group)</t>
+          <t>Pull&amp;Bear Kuwait (Alshaya)</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>https://www.splashfashions.com/kw/</t>
+          <t>https://www.pullandbear.com/kw/</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Amit Maheshwari</t>
+          <t>Maëlle Mandjee (Basselot)</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Head of Ecommerce, Centrepoint (Landmark Group, GCC)</t>
+          <t>Director of Ecommerce, Alshaya Group</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -17148,29 +17155,29 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/amit-maheshwari-124675</t>
+          <t>https://www.linkedin.com/in/ma%C3%ABlle-basselot</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
         <is>
-          <t>Bloomingdale's (Al Tayer Insignia)</t>
+          <t>offersonly</t>
         </is>
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>https://bloomingdales.ae/</t>
+          <t>https://www.offersonly.com.kw/</t>
         </is>
       </c>
       <c r="C203" s="5" t="inlineStr">
         <is>
-          <t>Khalid Al Tayer</t>
+          <t>Shaimaa Samir</t>
         </is>
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO, Ounass; Managing Director, Al Tayer Insignia (operates Bloomingdale's Kuwait)</t>
+          <t>Marketing Manager (Pharmalife / AlDaweya group)</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
@@ -17185,29 +17192,29 @@
       </c>
       <c r="G203" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/khalid-al-tayer-689140</t>
+          <t>https://linkedin.com/in/shimaasamir282</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>COS Kuwait (Alshaya)</t>
+          <t>Behbehani Watch World</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>https://kw.cos.com/</t>
+          <t>https://www.behbehaniwatchworld.com.kw/</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Khuzema Saifuddin</t>
+          <t>Mohammed AlKassas</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>eCommerce Lead, Alshaya Group (Kuwait)</t>
+          <t>General Manager Watches &amp; Jewelry, Mohammad Saleh &amp; Reza Yousuf Behbehani Co. (Behbehani Watch World)</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -17222,29 +17229,29 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/khuzema-saifuddin-534922a6</t>
+          <t>https://linkedin.com/in/mohammedqassas</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="5" t="inlineStr">
         <is>
-          <t>COS Kuwait (Alshaya)</t>
+          <t>مجوهرات داماس</t>
         </is>
       </c>
       <c r="B205" s="6" t="inlineStr">
         <is>
-          <t>https://kw.cos.com/</t>
+          <t>https://www.damasjewellery.com/kw-ar/</t>
         </is>
       </c>
       <c r="C205" s="5" t="inlineStr">
         <is>
-          <t>Rob Silsbury</t>
+          <t>Shashank Shobhit</t>
         </is>
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>Vice President Ecommerce, Alshaya Group (all brand websites/apps across MENA)</t>
+          <t>Head of Ecommerce, Damas Jewellery</t>
         </is>
       </c>
       <c r="E205" s="5" t="inlineStr">
@@ -17259,29 +17266,29 @@
       </c>
       <c r="G205" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/robsilsbury</t>
+          <t>https://linkedin.com/in/shashank-shobhit-49579655</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>COS Kuwait (Alshaya)</t>
+          <t>مجوهرات داماس</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>https://kw.cos.com/</t>
+          <t>https://www.damasjewellery.com/kw-ar/</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Maëlle Mandjee (Basselot)</t>
+          <t>Amna Omer</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Director of Ecommerce, Alshaya Group</t>
+          <t>Senior Digital Marketing Lead (GCC), Damas Jewellery</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -17296,29 +17303,29 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ma%C3%ABlle-basselot</t>
+          <t>https://ae.linkedin.com/in/amna-omer</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="5" t="inlineStr">
         <is>
-          <t>DKNY Kuwait (Alyasra Fashion)</t>
+          <t>MY COLORS</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>https://dkny.com.kw/</t>
+          <t>https://mycolors.com/</t>
         </is>
       </c>
       <c r="C207" s="5" t="inlineStr">
         <is>
-          <t>Phillip Smith</t>
+          <t>Hazem Hasna</t>
         </is>
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>Digital &amp; Ecommerce Director, Alyasra Fashion (GCC: DKNY, Cole Haan, Allbirds, Banana Republic, Ontime etc.)</t>
+          <t>General Manager, District General Trading &amp; Contracting Co. (My Colors)</t>
         </is>
       </c>
       <c r="E207" s="5" t="inlineStr">
@@ -17333,29 +17340,29 @@
       </c>
       <c r="G207" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/phillip-smith-9aa91a44</t>
+          <t>https://linkedin.com/in/hazemhasna</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>DKNY Kuwait (Alyasra Fashion)</t>
+          <t>MY COLORS</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>https://dkny.com.kw/</t>
+          <t>https://mycolors.com/</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Dexter Fernandes</t>
+          <t>Abdul Majid Madi</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>E-commerce Manager, Alyasra Fashion (Kuwait)</t>
+          <t>Founder &amp; CEO, District General Trading &amp; Contracting Co. (My Colors)</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -17370,29 +17377,29 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>https://kw.linkedin.com/in/dexter-fernandes-2783ab113</t>
+          <t>https://linkedin.com/in/abdul-majid-madi-631712133</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
         <is>
-          <t>DKNY Kuwait (Alyasra Fashion)</t>
+          <t>MY COLORS</t>
         </is>
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>https://dkny.com.kw/</t>
+          <t>https://www.mycolors.com/en/kw/</t>
         </is>
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>Eudgen Padin Gempesao</t>
+          <t>Hazem Hasna</t>
         </is>
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>Ecommerce Operations Specialist, Alyasra Fashion (Ontime, DKNY, Cole Haan, Allbirds; Kuwait-KSA-UAE-Bahrain)</t>
+          <t>General Manager, District General Trading &amp; Contracting Co. (My Colors)</t>
         </is>
       </c>
       <c r="E209" s="5" t="inlineStr">
@@ -17407,29 +17414,29 @@
       </c>
       <c r="G209" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/eudgen-padin-gempesao-1086b111b</t>
+          <t>https://linkedin.com/in/hazemhasna</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>H&amp;S Store</t>
+          <t>MY COLORS</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>https://hsstore.com/</t>
+          <t>https://www.mycolors.com/en/kw/</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Fahad Almethen</t>
+          <t>Abdul Majid Madi</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Founder and CEO of H&amp;S Store</t>
+          <t>Founder &amp; CEO, District General Trading &amp; Contracting Co. (My Colors)</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -17444,29 +17451,29 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/fahad-almethen-5373a118a</t>
+          <t>https://linkedin.com/in/abdul-majid-madi-631712133</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
         <is>
-          <t>Roots Roastery</t>
+          <t>Muji</t>
         </is>
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
-          <t>https://rootsroastery.net/</t>
+          <t>https://www.muji.com.kw/</t>
         </is>
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>Hasan Alkandari</t>
+          <t>Rob Silsbury</t>
         </is>
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>Co-founder | Roots Roastery</t>
+          <t>Vice President Ecommerce, Alshaya Group (all brand websites/apps across MENA)</t>
         </is>
       </c>
       <c r="E211" s="5" t="inlineStr">
@@ -17481,29 +17488,29 @@
       </c>
       <c r="G211" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/hasan-alkandari-804359245</t>
+          <t>https://www.linkedin.com/in/robsilsbury</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>Roots Roastery</t>
+          <t>Splash Kuwait (Landmark Group)</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>https://rootsroastery.net/</t>
+          <t>https://www.splashfashions.com/kw/</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Abdulrahman Al Daihani</t>
+          <t>Reddy Prasad</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>CEO ROOTS ROASTERY CO</t>
+          <t>Manager E-Commerce (Associate General Manager E-Commerce), Landmark Group Kuwait</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -17518,29 +17525,29 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/abdulrahman-al-daihani-62baab288</t>
+          <t>https://www.linkedin.com/in/reddy-prasad-a20b5358</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
         <is>
-          <t>Milano Kuwait (Alshaya)</t>
+          <t>Splash Kuwait (Landmark Group)</t>
         </is>
       </c>
       <c r="B213" s="6" t="inlineStr">
         <is>
-          <t>https://kuwait.milanomena.com/</t>
+          <t>https://www.splashfashions.com/kw/</t>
         </is>
       </c>
       <c r="C213" s="5" t="inlineStr">
         <is>
-          <t>Khuzema Saifuddin</t>
+          <t>Amit Maheshwari</t>
         </is>
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>eCommerce Lead, Alshaya Group (Kuwait)</t>
+          <t>Head of Ecommerce, Centrepoint (Landmark Group, GCC)</t>
         </is>
       </c>
       <c r="E213" s="5" t="inlineStr">
@@ -17555,29 +17562,29 @@
       </c>
       <c r="G213" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/khuzema-saifuddin-534922a6</t>
+          <t>https://www.linkedin.com/in/amit-maheshwari-124675</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>Milano Kuwait (Alshaya)</t>
+          <t>MF Food</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>https://kuwait.milanomena.com/</t>
+          <t>https://mf-food.com.kw/</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Rob Silsbury</t>
+          <t>Abdulwahab Alessa</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Vice President Ecommerce, Alshaya Group (all brand websites/apps across MENA)</t>
+          <t>General Manager, MF Food</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -17592,29 +17599,29 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/robsilsbury</t>
+          <t>https://linkedin.com/in/abdulwahab-alessa-56498a84</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
         <is>
-          <t>Milano Kuwait (Alshaya)</t>
+          <t>Ooredoo Kuwait Online Store</t>
         </is>
       </c>
       <c r="B215" s="6" t="inlineStr">
         <is>
-          <t>https://kuwait.milanomena.com/</t>
+          <t>https://store.ooredoo.com.kw/</t>
         </is>
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>Maëlle Mandjee (Basselot)</t>
+          <t>Nikhil Kosuri</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>Director of Ecommerce, Alshaya Group</t>
+          <t>Director of Digital, Ooredoo Kuwait</t>
         </is>
       </c>
       <c r="E215" s="5" t="inlineStr">
@@ -17627,31 +17634,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G215" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/ma%C3%ABlle-basselot</t>
+      <c r="G215" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>Mubkhar</t>
+          <t>Ooredoo Kuwait Online Store</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>https://kw.mubkhar.com/</t>
+          <t>https://store.ooredoo.com.kw/</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Emad Ghali</t>
+          <t>Htar Thant Zin</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>mubkhar Group Operations Director</t>
+          <t>Chief Commercial Officer, Ooredoo Kuwait</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -17664,31 +17671,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G216" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/emad-ghali-525a91112</t>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
         <is>
-          <t>Allbirds Kuwait (Alyasra Fashion)</t>
+          <t>Ooredoo Kuwait Online Store</t>
         </is>
       </c>
       <c r="B217" s="6" t="inlineStr">
         <is>
-          <t>https://allbirds.com.kw/</t>
+          <t>https://store.ooredoo.com.kw/</t>
         </is>
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>Phillip Smith</t>
+          <t>Abdulaziz Al-Babtain</t>
         </is>
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>Digital &amp; Ecommerce Director, Alyasra Fashion (GCC: DKNY, Cole Haan, Allbirds, Banana Republic, Ontime etc.)</t>
+          <t>Chief Executive Officer, Ooredoo Kuwait</t>
         </is>
       </c>
       <c r="E217" s="5" t="inlineStr">
@@ -17701,31 +17708,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G217" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/phillip-smith-9aa91a44</t>
+      <c r="G217" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>Allbirds Kuwait (Alyasra Fashion)</t>
+          <t>WaleedToys</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>https://allbirds.com.kw/</t>
+          <t>https://www.waleedtoys.com/</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Dexter Fernandes</t>
+          <t>Mohamed Aref</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>E-commerce Manager, Alyasra Fashion (Kuwait)</t>
+          <t>Ecommerce Manager</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -17740,29 +17747,29 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>https://kw.linkedin.com/in/dexter-fernandes-2783ab113</t>
+          <t>https://linkedin.com/in/mohamed-aref-81b112239</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
         <is>
-          <t>Allbirds Kuwait (Alyasra Fashion)</t>
+          <t>WaleedToys</t>
         </is>
       </c>
       <c r="B219" s="6" t="inlineStr">
         <is>
-          <t>https://allbirds.com.kw/</t>
+          <t>https://www.waleedtoys.com/</t>
         </is>
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>Eudgen Padin Gempesao</t>
+          <t>Ali Ahmed</t>
         </is>
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>Ecommerce Operations Specialist, Alyasra Fashion (Ontime, DKNY, Cole Haan, Allbirds; Kuwait-KSA-UAE-Bahrain)</t>
+          <t>Senior Operations Manager (Waleed Toys &amp; Gifts Co.)</t>
         </is>
       </c>
       <c r="E219" s="5" t="inlineStr">
@@ -17777,29 +17784,29 @@
       </c>
       <c r="G219" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/eudgen-padin-gempesao-1086b111b</t>
+          <t>https://linkedin.com/in/ali-ahmed895</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>Babyshop Kuwait (Landmark Group)</t>
+          <t>Al Sirhan Shoes</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>https://www.babyshopstores.com/kw/</t>
+          <t>https://shop.alsirhanshoes.com/</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Reddy Prasad</t>
+          <t>Mohamad Barada</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Manager E-Commerce (Associate General Manager E-Commerce), Landmark Group Kuwait</t>
+          <t>Marketing E-commerce &amp; Concept Manager, Al Sirhan Shoes</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -17814,29 +17821,29 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/reddy-prasad-a20b5358</t>
+          <t>https://linkedin.com/in/mohamad-barada-6b1bb55a</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
         <is>
-          <t>Babyshop Kuwait (Landmark Group)</t>
+          <t>Al Sirhan Shoes</t>
         </is>
       </c>
       <c r="B221" s="6" t="inlineStr">
         <is>
-          <t>https://www.babyshopstores.com/kw/</t>
+          <t>https://shop.alsirhanshoes.com/</t>
         </is>
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>Amit Maheshwari</t>
+          <t>Fadi Atef Soufan</t>
         </is>
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>Head of Ecommerce, Centrepoint (Landmark Group, GCC)</t>
+          <t>CEO, Al Sirhan Shoes / AlSirhan Holding</t>
         </is>
       </c>
       <c r="E221" s="5" t="inlineStr">
@@ -17851,29 +17858,29 @@
       </c>
       <c r="G221" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/amit-maheshwari-124675</t>
+          <t>https://linkedin.com/in/fadi-soufan-8687b031</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>BJ BEAUTY</t>
+          <t>Al Sirhan Shoes</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>https://www.bjbeauty.co/</t>
+          <t>https://shop.alsirhanshoes.com/</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Abdullah Jumma</t>
+          <t>Darran Carter</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Managing Director at BJ Beauty</t>
+          <t>General Manager, Al Sirhan Shoes</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -17888,29 +17895,29 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/abdullah-jumma-a8a84696</t>
+          <t>https://linkedin.com/in/darran-carter-a1b08558</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>Drops</t>
+          <t>Al Sirhan Shoes</t>
         </is>
       </c>
       <c r="B223" s="6" t="inlineStr">
         <is>
-          <t>https://drops.me/en-kw/</t>
+          <t>https://shop.alsirhanshoes.com/</t>
         </is>
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>Saud Al Sumait, CFA</t>
+          <t>Ahmed Khaled Al Sirhan</t>
         </is>
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>Deputy CEO at Drops Application</t>
+          <t>Owner, Al Sirhan Shoes</t>
         </is>
       </c>
       <c r="E223" s="5" t="inlineStr">
@@ -17923,31 +17930,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G223" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/salsumait</t>
+      <c r="G223" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>Digits</t>
+          <t>Bloomingdale's (Al Tayer Insignia)</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>https://digits.com.kw/</t>
+          <t>https://bloomingdales.ae/</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Fawaz Katfa</t>
+          <t>Khalid Al Tayer</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Deputy General Manager DIGITS Apple Reseller</t>
+          <t>Founder &amp; CEO, Ounass; Managing Director, Al Tayer Insignia (operates Bloomingdale's Kuwait)</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -17962,29 +17969,29 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/fawaz-katfa-7a298485</t>
+          <t>https://www.linkedin.com/in/khalid-al-tayer-689140</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="5" t="inlineStr">
         <is>
-          <t>YesStyle</t>
+          <t>Pro Sports</t>
         </is>
       </c>
       <c r="B225" s="6" t="inlineStr">
         <is>
-          <t>https://www.yesstyle.com/</t>
+          <t>https://www.prosportskw.com/</t>
         </is>
       </c>
       <c r="C225" s="5" t="inlineStr">
         <is>
-          <t>Joshua Lau</t>
+          <t>Asif Juzar</t>
         </is>
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
-          <t>Co-founder &amp; CEO, YesStyle.com</t>
+          <t>Founder, Pro Sports Kuwait (Professional Sports General Trading Co.)</t>
         </is>
       </c>
       <c r="E225" s="5" t="inlineStr">
@@ -17999,66 +18006,66 @@
       </c>
       <c r="G225" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/joshualau</t>
+          <t>https://linkedin.com/in/asifjuzar</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>Squatwolf Kuwait (AAW franchise)</t>
+          <t>Pro Sports</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>https://squatwolf.com/en-kw/</t>
+          <t>https://www.prosportskw.com/</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Louay Baalbaky</t>
+          <t>Abbas Hussaini</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Sr. Brand Manager - Intersport &amp; Squatwolf (Kuwait), AAW</t>
+          <t>Digital Marketing Manager, Pro Sports Kuwait</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>+965 22088577</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="G226" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/louay-baalbaky-47626b29</t>
+          <t>info@prosportskw.com</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
         <is>
-          <t>Squatwolf Kuwait (AAW franchise)</t>
+          <t>MAGRABi Kuwait</t>
         </is>
       </c>
       <c r="B227" s="6" t="inlineStr">
         <is>
-          <t>https://squatwolf.com/en-kw/</t>
+          <t>https://www.magrabi.com/kw-en/</t>
         </is>
       </c>
       <c r="C227" s="5" t="inlineStr">
         <is>
-          <t>Murtaza Fakhruddin</t>
+          <t>Yasser Taher</t>
         </is>
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>Senior Projects Manager - Ecommerce, Ali Abdulwahab Al Mutawa Commercial Co. (AAW) (LinkedIn headline; experience entry still lists Head of Ecommerce since Mar 2020)</t>
+          <t>Chief Executive Officer, MAGRABi Retail Group</t>
         </is>
       </c>
       <c r="E227" s="5" t="inlineStr">
@@ -18071,31 +18078,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G227" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/murtaza-fakhruddin-0692681b</t>
+      <c r="G227" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>Squatwolf Kuwait (AAW franchise)</t>
+          <t>MAGRABi Kuwait</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>https://squatwolf.com/en-kw/</t>
+          <t>https://www.magrabi.com/kw-en/</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Hala Thiab</t>
+          <t>Shorouk Mahboub</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Senior eCommerce Manager, Ali Abdulwahab Al Mutawa Commercial Co. (AAW) (Sep 2020-present)</t>
+          <t>Regional Omnichannel &amp; Operational Business Adviser, MAGRABi Retail Group</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -18110,29 +18117,29 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/hala-thiab-44a60956</t>
+          <t>https://linkedin.com/in/shorouk-mahboub</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="5" t="inlineStr">
         <is>
-          <t>Petsmarket</t>
+          <t>B2B Foodstuff Kuwait</t>
         </is>
       </c>
       <c r="B229" s="6" t="inlineStr">
         <is>
-          <t>https://www.petsmarket.com/</t>
+          <t>https://b2bfoods.com/</t>
         </is>
       </c>
       <c r="C229" s="5" t="inlineStr">
         <is>
-          <t>Khalid R. AlBader</t>
+          <t>Nasir Mucedidi</t>
         </is>
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>Chairman &amp; Founder at PetsMarket.com</t>
+          <t>Founder &amp; CEO</t>
         </is>
       </c>
       <c r="E229" s="5" t="inlineStr">
@@ -18147,29 +18154,29 @@
       </c>
       <c r="G229" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/khalid-r-albader-3a14ab105</t>
+          <t>https://linkedin.com/in/nasir-mucedidi-62aa273a</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>Zue</t>
+          <t>COS Kuwait (Alshaya)</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>https://www.zue.com.kw/</t>
+          <t>https://kw.cos.com/</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Mohammad Almutawa</t>
+          <t>Khuzema Saifuddin</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer at Zue for pet</t>
+          <t>eCommerce Lead, Alshaya Group (Kuwait)</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -18184,49 +18191,3305 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mohammad-almutawa-a48a11b9</t>
+          <t>https://www.linkedin.com/in/khuzema-saifuddin-534922a6</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="5" t="inlineStr">
         <is>
+          <t>COS Kuwait (Alshaya)</t>
+        </is>
+      </c>
+      <c r="B231" s="6" t="inlineStr">
+        <is>
+          <t>https://kw.cos.com/</t>
+        </is>
+      </c>
+      <c r="C231" s="5" t="inlineStr">
+        <is>
+          <t>Rob Silsbury</t>
+        </is>
+      </c>
+      <c r="D231" s="5" t="inlineStr">
+        <is>
+          <t>Vice President Ecommerce, Alshaya Group (all brand websites/apps across MENA)</t>
+        </is>
+      </c>
+      <c r="E231" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F231" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G231" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/robsilsbury</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>COS Kuwait (Alshaya)</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>https://kw.cos.com/</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>Maëlle Mandjee (Basselot)</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>Director of Ecommerce, Alshaya Group</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G232" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ma%C3%ABlle-basselot</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="5" t="inlineStr">
+        <is>
+          <t>DKNY Kuwait (Alyasra Fashion)</t>
+        </is>
+      </c>
+      <c r="B233" s="6" t="inlineStr">
+        <is>
+          <t>https://dkny.com.kw/</t>
+        </is>
+      </c>
+      <c r="C233" s="5" t="inlineStr">
+        <is>
+          <t>Phillip Smith</t>
+        </is>
+      </c>
+      <c r="D233" s="5" t="inlineStr">
+        <is>
+          <t>Digital &amp; Ecommerce Director, Alyasra Fashion (GCC: DKNY, Cole Haan, Allbirds, Banana Republic, Ontime etc.)</t>
+        </is>
+      </c>
+      <c r="E233" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F233" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G233" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/phillip-smith-9aa91a44</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>DKNY Kuwait (Alyasra Fashion)</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>https://dkny.com.kw/</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>Dexter Fernandes</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>E-commerce Manager, Alyasra Fashion (Kuwait)</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G234" s="3" t="inlineStr">
+        <is>
+          <t>https://kw.linkedin.com/in/dexter-fernandes-2783ab113</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="5" t="inlineStr">
+        <is>
+          <t>DKNY Kuwait (Alyasra Fashion)</t>
+        </is>
+      </c>
+      <c r="B235" s="6" t="inlineStr">
+        <is>
+          <t>https://dkny.com.kw/</t>
+        </is>
+      </c>
+      <c r="C235" s="5" t="inlineStr">
+        <is>
+          <t>Eudgen Padin Gempesao</t>
+        </is>
+      </c>
+      <c r="D235" s="5" t="inlineStr">
+        <is>
+          <t>Ecommerce Operations Specialist, Alyasra Fashion (Ontime, DKNY, Cole Haan, Allbirds; Kuwait-KSA-UAE-Bahrain)</t>
+        </is>
+      </c>
+      <c r="E235" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F235" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G235" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/eudgen-padin-gempesao-1086b111b</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>تسوقوا أحذية فاخرة وحقائب وإكسسوارات من متجر ليفيل شوز الكويت</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>https://ar-kuwait.levelshoes.com/</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>Lynn Abiad</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>General Manager, Ecommerce - Level Shoes (Chalhoub Group)</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G236" s="3" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/in/lynnabiad</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="5" t="inlineStr">
+        <is>
+          <t>تسوقوا أحذية فاخرة وحقائب وإكسسوارات من متجر ليفيل شوز الكويت</t>
+        </is>
+      </c>
+      <c r="B237" s="6" t="inlineStr">
+        <is>
+          <t>https://ar-kuwait.levelshoes.com/</t>
+        </is>
+      </c>
+      <c r="C237" s="5" t="inlineStr">
+        <is>
+          <t>Elisa Bruno</t>
+        </is>
+      </c>
+      <c r="D237" s="5" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer, Level Shoes</t>
+        </is>
+      </c>
+      <c r="E237" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F237" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G237" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>H&amp;S Store</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>https://hsstore.com/</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>Fahad Almethen</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>Founder and CEO of H&amp;S Store</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G238" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fahad-almethen-5373a118a</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="5" t="inlineStr">
+        <is>
+          <t>Mumzworld</t>
+        </is>
+      </c>
+      <c r="B239" s="6" t="inlineStr">
+        <is>
+          <t>https://www.mumzworld.com/kw-en/</t>
+        </is>
+      </c>
+      <c r="C239" s="5" t="inlineStr">
+        <is>
+          <t>Hasan Ebrahim</t>
+        </is>
+      </c>
+      <c r="D239" s="5" t="inlineStr">
+        <is>
+          <t>Country Head (GCC incl. KSA, UAE, Qatar, Bahrain), Mumzworld</t>
+        </is>
+      </c>
+      <c r="E239" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F239" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G239" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/h89ebrahim</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>Mumzworld</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mumzworld.com/kw-en/</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>Chirin Khawatmi</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>Chief Brand Officer, Mumzworld</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G240" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/chirin-khawatmi</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="5" t="inlineStr">
+        <is>
+          <t>Mumzworld</t>
+        </is>
+      </c>
+      <c r="B241" s="6" t="inlineStr">
+        <is>
+          <t>https://www.mumzworld.com/kw-en/</t>
+        </is>
+      </c>
+      <c r="C241" s="5" t="inlineStr">
+        <is>
+          <t>Massimiliano Spalazzi</t>
+        </is>
+      </c>
+      <c r="D241" s="5" t="inlineStr">
+        <is>
+          <t>Group CEO, Mumzworld</t>
+        </is>
+      </c>
+      <c r="E241" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F241" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G241" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/massimilianospalazzi</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>L’Occitane Kuwait</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>https://kw.loccitane.com/</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>Mariana Gaspar Rodrigues</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>Marketing &amp; F&amp;B Director - Middle East, L'Occitane Group (incl. Kuwait retail &amp; e-commerce)</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G242" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/mariana-gaspar-rodrigues-14692512</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="5" t="inlineStr">
+        <is>
+          <t>L’Occitane Kuwait</t>
+        </is>
+      </c>
+      <c r="B243" s="6" t="inlineStr">
+        <is>
+          <t>https://kw.loccitane.com/</t>
+        </is>
+      </c>
+      <c r="C243" s="5" t="inlineStr">
+        <is>
+          <t>Daniele Bueno</t>
+        </is>
+      </c>
+      <c r="D243" s="5" t="inlineStr">
+        <is>
+          <t>Head of Retail and Wholesale - Middle East, L'Occitane Group</t>
+        </is>
+      </c>
+      <c r="E243" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F243" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G243" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/daniele-bueno-42a0ba33</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>L’Occitane Kuwait</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>https://kw.loccitane.com/</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>Walaa Moussa</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>Retail Manager, L'Occitane Kuwait</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G244" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/walaa-moussa-8bbab2110</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="5" t="inlineStr">
+        <is>
+          <t>U.S. Polo Assn. Kuwait</t>
+        </is>
+      </c>
+      <c r="B245" s="6" t="inlineStr">
+        <is>
+          <t>https://www.uspoloassn.com.kw/</t>
+        </is>
+      </c>
+      <c r="C245" s="5" t="inlineStr">
+        <is>
+          <t>Amir Al-Hinnawi</t>
+        </is>
+      </c>
+      <c r="D245" s="5" t="inlineStr">
+        <is>
+          <t>Managing Partner Kuwait &amp; Lebanon, Starco Holding; CEO, Bevava (e-commerce platform for Starco franchised brands)</t>
+        </is>
+      </c>
+      <c r="E245" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F245" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G245" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/amiralhinnawi</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Polo Assn. Kuwait</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>https://www.uspoloassn.com.kw/</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>Mohamad Hadi</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>Brands Manager (U.S. Polo Assn., Benetton, Eden Park), Starco Holding</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G246" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/mohamad-hadi-140730a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="5" t="inlineStr">
+        <is>
+          <t>U.S. Polo Assn. Kuwait</t>
+        </is>
+      </c>
+      <c r="B247" s="6" t="inlineStr">
+        <is>
+          <t>https://www.uspoloassn.com.kw/</t>
+        </is>
+      </c>
+      <c r="C247" s="5" t="inlineStr">
+        <is>
+          <t>Jamal Al-Hinnawi</t>
+        </is>
+      </c>
+      <c r="D247" s="5" t="inlineStr">
+        <is>
+          <t>President &amp; CEO, Starco Holding</t>
+        </is>
+      </c>
+      <c r="E247" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F247" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G247" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/jamal-al-hinnawi-1ba8619</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>Sporter</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sporter.com/en-kw/</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>Osama Ishak</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Manager</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G248" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/osamaishak</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="5" t="inlineStr">
+        <is>
+          <t>Sporter</t>
+        </is>
+      </c>
+      <c r="B249" s="6" t="inlineStr">
+        <is>
+          <t>https://www.sporter.com/en-kw/</t>
+        </is>
+      </c>
+      <c r="C249" s="5" t="inlineStr">
+        <is>
+          <t>Majd Khayzoran</t>
+        </is>
+      </c>
+      <c r="D249" s="5" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="E249" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F249" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G249" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/majd-khayzoran-64513913</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>Clarks Kuwait</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>https://www.clarksstores.com.kw/</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>Ahmed Ismail</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>Regional Head of E-Commerce (incl. Clarks GCC e-commerce), Jashanmal Group</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G250" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/ahmed-ismail-899350a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="5" t="inlineStr">
+        <is>
+          <t>Al Rajhi Bank Kuwait</t>
+        </is>
+      </c>
+      <c r="B251" s="6" t="inlineStr">
+        <is>
+          <t>https://www.alrajhibank.com.kw/</t>
+        </is>
+      </c>
+      <c r="C251" s="5" t="inlineStr">
+        <is>
+          <t>Jassim Ismaeil Al-Awadhi</t>
+        </is>
+      </c>
+      <c r="D251" s="5" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer, Al Rajhi Bank Kuwait</t>
+        </is>
+      </c>
+      <c r="E251" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F251" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G251" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/jassem-alawadhi-02549b20</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>Mogahwi Library Company</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mogahwi.com.kw/</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>Hamad Al-Mogahwi</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G252" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/hamad-al-mogahwi-99bb7910</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="5" t="inlineStr">
+        <is>
+          <t>Falcon Store</t>
+        </is>
+      </c>
+      <c r="B253" s="6" t="inlineStr">
+        <is>
+          <t>https://falcon.com.kw/</t>
+        </is>
+      </c>
+      <c r="C253" s="5" t="inlineStr">
+        <is>
+          <t>Mahmoud A.</t>
+        </is>
+      </c>
+      <c r="D253" s="5" t="inlineStr">
+        <is>
+          <t>Ecommerce &amp; Channels Operations Manager, DJI / Falcon Kuwait (New Market Company)</t>
+        </is>
+      </c>
+      <c r="E253" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F253" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G253" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/mbenabdelaziz</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>Telefonati</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>https://www.telefonati.com/</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>Denrod Tabuzo</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>Digital Marketing Specialist / Ecommerce Web Administrator</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G254" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/denrod-tabuzo-736976147</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="5" t="inlineStr">
+        <is>
+          <t>Pharmalife-KW</t>
+        </is>
+      </c>
+      <c r="B255" s="6" t="inlineStr">
+        <is>
+          <t>https://pharmalife-kw.com/</t>
+        </is>
+      </c>
+      <c r="C255" s="5" t="inlineStr">
+        <is>
+          <t>Shaimaa Samir</t>
+        </is>
+      </c>
+      <c r="D255" s="5" t="inlineStr">
+        <is>
+          <t>Marketing Manager (Pharmalife Kuwait)</t>
+        </is>
+      </c>
+      <c r="E255" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F255" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G255" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/shimaasamir282</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>Pharmalife-KW</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>https://pharmalife-kw.com/</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>Azzam Baroudi</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>Pharma Manager (Marketing dept.)</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G256" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/azzam-baroudi-15576a7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="5" t="inlineStr">
+        <is>
+          <t>Roots Roastery</t>
+        </is>
+      </c>
+      <c r="B257" s="6" t="inlineStr">
+        <is>
+          <t>https://rootsroastery.net/</t>
+        </is>
+      </c>
+      <c r="C257" s="5" t="inlineStr">
+        <is>
+          <t>Hasan Alkandari</t>
+        </is>
+      </c>
+      <c r="D257" s="5" t="inlineStr">
+        <is>
+          <t>Co-founder | Roots Roastery</t>
+        </is>
+      </c>
+      <c r="E257" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F257" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G257" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hasan-alkandari-804359245</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>Roots Roastery</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>https://rootsroastery.net/</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>Abdulrahman Al Daihani</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>CEO ROOTS ROASTERY CO</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G258" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/abdulrahman-al-daihani-62baab288</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="5" t="inlineStr">
+        <is>
+          <t>Milano Kuwait (Alshaya)</t>
+        </is>
+      </c>
+      <c r="B259" s="6" t="inlineStr">
+        <is>
+          <t>https://kuwait.milanomena.com/</t>
+        </is>
+      </c>
+      <c r="C259" s="5" t="inlineStr">
+        <is>
+          <t>Khuzema Saifuddin</t>
+        </is>
+      </c>
+      <c r="D259" s="5" t="inlineStr">
+        <is>
+          <t>eCommerce Lead, Alshaya Group (Kuwait)</t>
+        </is>
+      </c>
+      <c r="E259" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F259" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G259" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/khuzema-saifuddin-534922a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Milano Kuwait (Alshaya)</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>https://kuwait.milanomena.com/</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>Rob Silsbury</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>Vice President Ecommerce, Alshaya Group (all brand websites/apps across MENA)</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G260" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/robsilsbury</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="5" t="inlineStr">
+        <is>
+          <t>Milano Kuwait (Alshaya)</t>
+        </is>
+      </c>
+      <c r="B261" s="6" t="inlineStr">
+        <is>
+          <t>https://kuwait.milanomena.com/</t>
+        </is>
+      </c>
+      <c r="C261" s="5" t="inlineStr">
+        <is>
+          <t>Maëlle Mandjee (Basselot)</t>
+        </is>
+      </c>
+      <c r="D261" s="5" t="inlineStr">
+        <is>
+          <t>Director of Ecommerce, Alshaya Group</t>
+        </is>
+      </c>
+      <c r="E261" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F261" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G261" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ma%C3%ABlle-basselot</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>Jashanmal Kuwait</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>https://kw.jashanmal.com/</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>Ahmed Ismail</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>Regional Head of E-Commerce, Jashanmal Group</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G262" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/ahmed-ismail-899350a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="5" t="inlineStr">
+        <is>
+          <t>Jashanmal Kuwait</t>
+        </is>
+      </c>
+      <c r="B263" s="6" t="inlineStr">
+        <is>
+          <t>https://kw.jashanmal.com/</t>
+        </is>
+      </c>
+      <c r="C263" s="5" t="inlineStr">
+        <is>
+          <t>Bismil Razik</t>
+        </is>
+      </c>
+      <c r="D263" s="5" t="inlineStr">
+        <is>
+          <t>Digital Marketing Manager, Jashanmal Group (UAE, Kuwait, Bahrain e-commerce sites)</t>
+        </is>
+      </c>
+      <c r="E263" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F263" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G263" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/bismilrazik</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>Jashanmal Kuwait</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>https://kw.jashanmal.com/</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>Shuja Jashanmal</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>Partner &amp; CEO, Jashanmal Group</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G264" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/shujajashanmal</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="5" t="inlineStr">
+        <is>
+          <t>Jashanmal Kuwait</t>
+        </is>
+      </c>
+      <c r="B265" s="6" t="inlineStr">
+        <is>
+          <t>https://kw.jashanmal.com/</t>
+        </is>
+      </c>
+      <c r="C265" s="5" t="inlineStr">
+        <is>
+          <t>Tony Jashanmal</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="inlineStr">
+        <is>
+          <t>Group President, Jashanmal</t>
+        </is>
+      </c>
+      <c r="E265" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F265" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G265" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>eBaqala.com</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>https://ebaqala.com/</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>Muffaddal Kalla</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>CEO (e-baqala.com)</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G266" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/mufkuw</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="5" t="inlineStr">
+        <is>
+          <t>eBaqala.com</t>
+        </is>
+      </c>
+      <c r="B267" s="6" t="inlineStr">
+        <is>
+          <t>https://ebaqala.com/</t>
+        </is>
+      </c>
+      <c r="C267" s="5" t="inlineStr">
+        <is>
+          <t>Zoeb Hussain Badri</t>
+        </is>
+      </c>
+      <c r="D267" s="5" t="inlineStr">
+        <is>
+          <t>Founder, Al-Hakimi Supermarket (eBaqala parent store)</t>
+        </is>
+      </c>
+      <c r="E267" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F267" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G267" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>Mubkhar</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>https://kw.mubkhar.com/</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>Emad Ghali</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>mubkhar Group Operations Director</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G268" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/emad-ghali-525a91112</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="5" t="inlineStr">
+        <is>
+          <t>Allbirds Kuwait (Alyasra Fashion)</t>
+        </is>
+      </c>
+      <c r="B269" s="6" t="inlineStr">
+        <is>
+          <t>https://allbirds.com.kw/</t>
+        </is>
+      </c>
+      <c r="C269" s="5" t="inlineStr">
+        <is>
+          <t>Phillip Smith</t>
+        </is>
+      </c>
+      <c r="D269" s="5" t="inlineStr">
+        <is>
+          <t>Digital &amp; Ecommerce Director, Alyasra Fashion (GCC: DKNY, Cole Haan, Allbirds, Banana Republic, Ontime etc.)</t>
+        </is>
+      </c>
+      <c r="E269" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F269" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G269" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/phillip-smith-9aa91a44</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>Allbirds Kuwait (Alyasra Fashion)</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>https://allbirds.com.kw/</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>Dexter Fernandes</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>E-commerce Manager, Alyasra Fashion (Kuwait)</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G270" s="3" t="inlineStr">
+        <is>
+          <t>https://kw.linkedin.com/in/dexter-fernandes-2783ab113</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="5" t="inlineStr">
+        <is>
+          <t>Allbirds Kuwait (Alyasra Fashion)</t>
+        </is>
+      </c>
+      <c r="B271" s="6" t="inlineStr">
+        <is>
+          <t>https://allbirds.com.kw/</t>
+        </is>
+      </c>
+      <c r="C271" s="5" t="inlineStr">
+        <is>
+          <t>Eudgen Padin Gempesao</t>
+        </is>
+      </c>
+      <c r="D271" s="5" t="inlineStr">
+        <is>
+          <t>Ecommerce Operations Specialist, Alyasra Fashion (Ontime, DKNY, Cole Haan, Allbirds; Kuwait-KSA-UAE-Bahrain)</t>
+        </is>
+      </c>
+      <c r="E271" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F271" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G271" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/eudgen-padin-gempesao-1086b111b</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>Zayoom</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>https://zayoom.com/</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>Saleem Awad</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder &amp; Managing Director</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="5" t="inlineStr">
+        <is>
+          <t>Babyshop Kuwait (Landmark Group)</t>
+        </is>
+      </c>
+      <c r="B273" s="6" t="inlineStr">
+        <is>
+          <t>https://www.babyshopstores.com/kw/</t>
+        </is>
+      </c>
+      <c r="C273" s="5" t="inlineStr">
+        <is>
+          <t>Reddy Prasad</t>
+        </is>
+      </c>
+      <c r="D273" s="5" t="inlineStr">
+        <is>
+          <t>Manager E-Commerce (Associate General Manager E-Commerce), Landmark Group Kuwait</t>
+        </is>
+      </c>
+      <c r="E273" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F273" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G273" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/reddy-prasad-a20b5358</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>Babyshop Kuwait (Landmark Group)</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>https://www.babyshopstores.com/kw/</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>Amit Maheshwari</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>Head of Ecommerce, Centrepoint (Landmark Group, GCC)</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G274" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/amit-maheshwari-124675</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="5" t="inlineStr">
+        <is>
+          <t>LUSH</t>
+        </is>
+      </c>
+      <c r="B275" s="6" t="inlineStr">
+        <is>
+          <t>https://lushkw.com/</t>
+        </is>
+      </c>
+      <c r="C275" s="5" t="inlineStr">
+        <is>
+          <t>Mariam Mohammad</t>
+        </is>
+      </c>
+      <c r="D275" s="5" t="inlineStr">
+        <is>
+          <t>Marketing and Public Relations Manager, LUSH Kuwait</t>
+        </is>
+      </c>
+      <c r="E275" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F275" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G275" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/mariam-mohammad-840164226</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>LUSH</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
+          <t>https://lushkw.com/</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>Miche Whitehouse</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>Regional Brand and Digital Manager - MENA, LUSH Fresh Handmade Cosmetics</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G276" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/miche-whitehouse-0534555a</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="5" t="inlineStr">
+        <is>
+          <t>Off Road Performance</t>
+        </is>
+      </c>
+      <c r="B277" s="6" t="inlineStr">
+        <is>
+          <t>https://orp.com.kw/</t>
+        </is>
+      </c>
+      <c r="C277" s="5" t="inlineStr">
+        <is>
+          <t>Yousef Alnemah</t>
+        </is>
+      </c>
+      <c r="D277" s="5" t="inlineStr">
+        <is>
+          <t>Founder &amp; CEO, Off Road Performance (ORP)</t>
+        </is>
+      </c>
+      <c r="E277" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F277" s="5" t="inlineStr">
+        <is>
+          <t>online@orp.com.kw</t>
+        </is>
+      </c>
+      <c r="G277" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/yousef-alnemah-34b566124</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>BJ BEAUTY</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bjbeauty.co/</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>Abdullah Jumma</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director at BJ Beauty</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G278" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/abdullah-jumma-a8a84696</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="5" t="inlineStr">
+        <is>
+          <t>Junaid Perfumes - Kuwait</t>
+        </is>
+      </c>
+      <c r="B279" s="6" t="inlineStr">
+        <is>
+          <t>https://kw.junaidperfumes.com/</t>
+        </is>
+      </c>
+      <c r="C279" s="5" t="inlineStr">
+        <is>
+          <t>Anas Ismail</t>
+        </is>
+      </c>
+      <c r="D279" s="5" t="inlineStr">
+        <is>
+          <t>Head of E-commerce &amp; Performance, Junaid Perfumes</t>
+        </is>
+      </c>
+      <c r="E279" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F279" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G279" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/anasismail</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>Junaid Perfumes - Kuwait</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="inlineStr">
+        <is>
+          <t>https://kw.junaidperfumes.com/</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>Hamad Junaid</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director, Junaid Perfumes</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G280" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/hamad-junaid-bbb70929</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="5" t="inlineStr">
+        <is>
+          <t>Junaid Perfumes - Kuwait</t>
+        </is>
+      </c>
+      <c r="B281" s="6" t="inlineStr">
+        <is>
+          <t>https://kw.junaidperfumes.com/</t>
+        </is>
+      </c>
+      <c r="C281" s="5" t="inlineStr">
+        <is>
+          <t>Abdulla Junaid</t>
+        </is>
+      </c>
+      <c r="D281" s="5" t="inlineStr">
+        <is>
+          <t>Managing Director, Junaid Perfumes</t>
+        </is>
+      </c>
+      <c r="E281" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F281" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G281" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/abdulla-junaid-10b71a227</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>Eyewa</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>https://eyewa.com/kw-en/</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>Jean Thomas</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>CMO &amp; Chief Product/Tech Officer (marketing, eCommerce, product, tech - all GCC), Eyewa</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G282" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/jeanthomasfr</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="5" t="inlineStr">
+        <is>
+          <t>Eyewa</t>
+        </is>
+      </c>
+      <c r="B283" s="6" t="inlineStr">
+        <is>
+          <t>https://eyewa.com/kw-en/</t>
+        </is>
+      </c>
+      <c r="C283" s="5" t="inlineStr">
+        <is>
+          <t>Anass Boumediene</t>
+        </is>
+      </c>
+      <c r="D283" s="5" t="inlineStr">
+        <is>
+          <t>Co-CEO &amp; Co-Founder, Eyewa</t>
+        </is>
+      </c>
+      <c r="E283" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F283" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G283" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/boumediene</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>Eyewa</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t>https://eyewa.com/kw-en/</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>Mehdi Oudghiri</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>Co-CEO &amp; Co-Founder, Eyewa</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G284" s="3" t="inlineStr">
+        <is>
+          <t>https://ae.linkedin.com/in/mehdioudghiri</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="5" t="inlineStr">
+        <is>
+          <t>Drops</t>
+        </is>
+      </c>
+      <c r="B285" s="6" t="inlineStr">
+        <is>
+          <t>https://drops.me/en-kw/</t>
+        </is>
+      </c>
+      <c r="C285" s="5" t="inlineStr">
+        <is>
+          <t>Saud Al Sumait, CFA</t>
+        </is>
+      </c>
+      <c r="D285" s="5" t="inlineStr">
+        <is>
+          <t>Deputy CEO at Drops Application</t>
+        </is>
+      </c>
+      <c r="E285" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F285" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G285" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/salsumait</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Kuwait</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="inlineStr">
+        <is>
+          <t>https://kw.swissarabian.com/</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>Syed Adil Adnan</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>E-Commerce &amp; Digital Media Manager / Head of E-Commerce, Swiss Arabian Perfumes Group (group-level, Sharjah HQ)</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G286" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/syedadiladnan</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="5" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Kuwait</t>
+        </is>
+      </c>
+      <c r="B287" s="6" t="inlineStr">
+        <is>
+          <t>https://kw.swissarabian.com/</t>
+        </is>
+      </c>
+      <c r="C287" s="5" t="inlineStr">
+        <is>
+          <t>Alia Adam Ali</t>
+        </is>
+      </c>
+      <c r="D287" s="5" t="inlineStr">
+        <is>
+          <t>Marketing and Communications Manager, Swiss Arabian Perfumes Group (group-level)</t>
+        </is>
+      </c>
+      <c r="E287" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F287" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G287" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/alianabeel</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Kuwait</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>https://kw.swissarabian.com/</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>Nabeel Adam Ali</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>CEO &amp; Director, Swiss Arabian Perfumes Group</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="5" t="inlineStr">
+        <is>
+          <t>Game Store</t>
+        </is>
+      </c>
+      <c r="B289" s="6" t="inlineStr">
+        <is>
+          <t>https://gamestore.com.kw/</t>
+        </is>
+      </c>
+      <c r="C289" s="5" t="inlineStr">
+        <is>
+          <t>Falah Al-Ajmi</t>
+        </is>
+      </c>
+      <c r="D289" s="5" t="inlineStr">
+        <is>
+          <t>Owner, Co-founder &amp; CEO, Game Store</t>
+        </is>
+      </c>
+      <c r="E289" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F289" s="5" t="inlineStr">
+        <is>
+          <t>admin@gamestore.com.kw</t>
+        </is>
+      </c>
+      <c r="G289" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>Game Store</t>
+        </is>
+      </c>
+      <c r="B290" s="3" t="inlineStr">
+        <is>
+          <t>https://gamestore.com.kw/</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>Bashar Abdel Hamid</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>Head of Marketing, Game Store Company</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="5" t="inlineStr">
+        <is>
+          <t>Digits</t>
+        </is>
+      </c>
+      <c r="B291" s="6" t="inlineStr">
+        <is>
+          <t>https://digits.com.kw/</t>
+        </is>
+      </c>
+      <c r="C291" s="5" t="inlineStr">
+        <is>
+          <t>Fawaz Katfa</t>
+        </is>
+      </c>
+      <c r="D291" s="5" t="inlineStr">
+        <is>
+          <t>Deputy General Manager DIGITS Apple Reseller</t>
+        </is>
+      </c>
+      <c r="E291" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F291" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G291" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fawaz-katfa-7a298485</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>eMarket Kuwait: Discover Kuwait's Best Electronics</t>
+        </is>
+      </c>
+      <c r="B292" s="3" t="inlineStr">
+        <is>
+          <t>https://www.emarketkw.com/</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>Mohammed Sheikh Ibrahim (محمد شيخ ابراهيم)</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Manager, eMarket Kuwait (emarketkw.com)</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G292" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/%D9%85%D8%AD%D9%85%D8%AF-%D8%B4%D9%8A%D8%AE-%D8%A7%D8%A8%D8%B1%D8%A7%D9%87%D9%8A%D9%85-3a3256200</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="5" t="inlineStr">
+        <is>
+          <t>eMarket Kuwait: Discover Kuwait's Best Electronics</t>
+        </is>
+      </c>
+      <c r="B293" s="6" t="inlineStr">
+        <is>
+          <t>https://www.emarketkw.com/</t>
+        </is>
+      </c>
+      <c r="C293" s="5" t="inlineStr">
+        <is>
+          <t>Hossam Hassan</t>
+        </is>
+      </c>
+      <c r="D293" s="5" t="inlineStr">
+        <is>
+          <t>E-marketing Specialist &amp; Marketing Team Leader, eMarket Kuwait</t>
+        </is>
+      </c>
+      <c r="E293" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F293" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G293" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/hossam-hassan-3b1a0012</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>YesStyle</t>
+        </is>
+      </c>
+      <c r="B294" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yesstyle.com/</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>Joshua Lau</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder &amp; CEO, YesStyle.com</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G294" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/joshualau</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="5" t="inlineStr">
+        <is>
+          <t>The Face Shop</t>
+        </is>
+      </c>
+      <c r="B295" s="6" t="inlineStr">
+        <is>
+          <t>https://www.thefaceshop.com.kw/</t>
+        </is>
+      </c>
+      <c r="C295" s="5" t="inlineStr">
+        <is>
+          <t>Bodour Alhajji</t>
+        </is>
+      </c>
+      <c r="D295" s="5" t="inlineStr">
+        <is>
+          <t>CEO &amp; Founder, Skindollize (The Face Shop Kuwait)</t>
+        </is>
+      </c>
+      <c r="E295" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F295" s="5" t="inlineStr">
+        <is>
+          <t>ecommerce@skindollize.com</t>
+        </is>
+      </c>
+      <c r="G295" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/bodour-alhajji-2713bb82</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>The Face Shop</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>https://www.thefaceshop.com.kw/</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>Tariq Al Hajji</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder &amp; Managing Director, Skindollize (The Face Shop Kuwait)</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G296" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="5" t="inlineStr">
+        <is>
+          <t>The Face Shop</t>
+        </is>
+      </c>
+      <c r="B297" s="6" t="inlineStr">
+        <is>
+          <t>https://www.thefaceshop.com.kw/</t>
+        </is>
+      </c>
+      <c r="C297" s="5" t="inlineStr">
+        <is>
+          <t>Bashir Masri</t>
+        </is>
+      </c>
+      <c r="D297" s="5" t="inlineStr">
+        <is>
+          <t>General Manager, Skindollize (The Face Shop &amp; Skin Food)</t>
+        </is>
+      </c>
+      <c r="E297" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F297" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G297" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/bashir-masri-02812318</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>Ted Baker KW</t>
+        </is>
+      </c>
+      <c r="B298" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tedbaker.kw/</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>Micheline Berzy</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>Head of Marketing - Fashion Brands (Sandro, Maje, Claudie Pierlot, Ted Baker), Al-Futtaim</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G298" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/michelineberzy</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="5" t="inlineStr">
+        <is>
+          <t>Ted Baker KW</t>
+        </is>
+      </c>
+      <c r="B299" s="6" t="inlineStr">
+        <is>
+          <t>https://www.tedbaker.kw/</t>
+        </is>
+      </c>
+      <c r="C299" s="5" t="inlineStr">
+        <is>
+          <t>Sanja Gorgieva</t>
+        </is>
+      </c>
+      <c r="D299" s="5" t="inlineStr">
+        <is>
+          <t>Regional Brand Manager - Ted Baker (MENA), Al-Futtaim</t>
+        </is>
+      </c>
+      <c r="E299" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F299" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G299" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/sanja-gorgieva-b912a087</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>Sniggles</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
+          <t>https://sniggles.com.kw/</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>Fatima AlQattan</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>Owner / Founder, Sniggles Kuwait</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="5" t="inlineStr">
+        <is>
+          <t>Squatwolf Kuwait (AAW franchise)</t>
+        </is>
+      </c>
+      <c r="B301" s="6" t="inlineStr">
+        <is>
+          <t>https://squatwolf.com/en-kw/</t>
+        </is>
+      </c>
+      <c r="C301" s="5" t="inlineStr">
+        <is>
+          <t>Louay Baalbaky</t>
+        </is>
+      </c>
+      <c r="D301" s="5" t="inlineStr">
+        <is>
+          <t>Sr. Brand Manager - Intersport &amp; Squatwolf (Kuwait), AAW</t>
+        </is>
+      </c>
+      <c r="E301" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F301" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G301" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/louay-baalbaky-47626b29</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>Squatwolf Kuwait (AAW franchise)</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
+          <t>https://squatwolf.com/en-kw/</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>Murtaza Fakhruddin</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>Senior Projects Manager - Ecommerce, Ali Abdulwahab Al Mutawa Commercial Co. (AAW) (LinkedIn headline; experience entry still lists Head of Ecommerce since Mar 2020)</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G302" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/murtaza-fakhruddin-0692681b</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="5" t="inlineStr">
+        <is>
+          <t>Squatwolf Kuwait (AAW franchise)</t>
+        </is>
+      </c>
+      <c r="B303" s="6" t="inlineStr">
+        <is>
+          <t>https://squatwolf.com/en-kw/</t>
+        </is>
+      </c>
+      <c r="C303" s="5" t="inlineStr">
+        <is>
+          <t>Hala Thiab</t>
+        </is>
+      </c>
+      <c r="D303" s="5" t="inlineStr">
+        <is>
+          <t>Senior eCommerce Manager, Ali Abdulwahab Al Mutawa Commercial Co. (AAW) (Sep 2020-present)</t>
+        </is>
+      </c>
+      <c r="E303" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F303" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G303" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/hala-thiab-44a60956</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>أسواق يابو - الكويت</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
+          <t>https://yaboow.com/</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>Shemil Ay</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>General Manager &amp; Executive Director</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G304" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/shemil-ay-511bb817</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="5" t="inlineStr">
+        <is>
+          <t>Petsmarket</t>
+        </is>
+      </c>
+      <c r="B305" s="6" t="inlineStr">
+        <is>
+          <t>https://www.petsmarket.com/</t>
+        </is>
+      </c>
+      <c r="C305" s="5" t="inlineStr">
+        <is>
+          <t>Khalid R. AlBader</t>
+        </is>
+      </c>
+      <c r="D305" s="5" t="inlineStr">
+        <is>
+          <t>Chairman &amp; Founder at PetsMarket.com</t>
+        </is>
+      </c>
+      <c r="E305" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F305" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G305" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/khalid-r-albader-3a14ab105</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>Modish</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="inlineStr">
+        <is>
+          <t>https://modish.com.kw/</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>Sarah N. AlThekair</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder &amp; CEO</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="5" t="inlineStr">
+        <is>
+          <t>ستايلاتي</t>
+        </is>
+      </c>
+      <c r="B307" s="6" t="inlineStr">
+        <is>
+          <t>https://stylati.com/</t>
+        </is>
+      </c>
+      <c r="C307" s="5" t="inlineStr">
+        <is>
+          <t>Mohammed Barakat</t>
+        </is>
+      </c>
+      <c r="D307" s="5" t="inlineStr">
+        <is>
+          <t>Co-Founder &amp; CEO</t>
+        </is>
+      </c>
+      <c r="E307" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F307" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G307" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/mohammed-barakat-37492922</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>Jomla.ae</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
+          <t>https://jomla.ae/</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>Mohammed Al Zoubi</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder, E-Commerce &amp; Digital Marketing Manager</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G308" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/mohdalzoubi</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="5" t="inlineStr">
+        <is>
+          <t>Jomla.ae</t>
+        </is>
+      </c>
+      <c r="B309" s="6" t="inlineStr">
+        <is>
+          <t>https://jomla.ae/</t>
+        </is>
+      </c>
+      <c r="C309" s="5" t="inlineStr">
+        <is>
+          <t>Adnan Seif Aldeen</t>
+        </is>
+      </c>
+      <c r="D309" s="5" t="inlineStr">
+        <is>
+          <t>Co-Founder &amp; General Manager</t>
+        </is>
+      </c>
+      <c r="E309" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F309" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G309" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/adnan-seif-aldeen-63b870213</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>Hilti Homepage</t>
+        </is>
+      </c>
+      <c r="B310" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hilti.com.kw/</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>Hamed Zaghloul</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Manager, Hilti Kuwait</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G310" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/hamed-zaghloul-ba6632128</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="5" t="inlineStr">
+        <is>
+          <t>Hilti Homepage</t>
+        </is>
+      </c>
+      <c r="B311" s="6" t="inlineStr">
+        <is>
+          <t>https://www.hilti.com.kw/</t>
+        </is>
+      </c>
+      <c r="C311" s="5" t="inlineStr">
+        <is>
+          <t>Mamdouh Barafi</t>
+        </is>
+      </c>
+      <c r="D311" s="5" t="inlineStr">
+        <is>
+          <t>Country Manager, Hilti Kuwait</t>
+        </is>
+      </c>
+      <c r="E311" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F311" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G311" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/mamdouh-barafi-901a7747</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>Naos Care Kuwait</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="inlineStr">
+        <is>
+          <t>https://naos.com.kw/</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>Rania Mahmoud</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Manager Kuwait, NAOS (Bioderma, Institut Esthederm, Etat Pur)</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G312" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/rania-mahmoud-1a660b3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="5" t="inlineStr">
+        <is>
+          <t>Naos Care Kuwait</t>
+        </is>
+      </c>
+      <c r="B313" s="6" t="inlineStr">
+        <is>
+          <t>https://naos.com.kw/</t>
+        </is>
+      </c>
+      <c r="C313" s="5" t="inlineStr">
+        <is>
+          <t>Donia Aisar</t>
+        </is>
+      </c>
+      <c r="D313" s="5" t="inlineStr">
+        <is>
+          <t>Marketing and E-commerce Specialist, NAOS Kuwait</t>
+        </is>
+      </c>
+      <c r="E313" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F313" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G313" s="6" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/donia-aisar-b39088232</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>Naos Care Kuwait</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="inlineStr">
+        <is>
+          <t>https://naos.com.kw/</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>Hamed Agina</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>Area Director Middle East (Distribution), NAOS</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G314" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/hamed-agina-25a62664</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="5" t="inlineStr">
+        <is>
+          <t>Time Keeper</t>
+        </is>
+      </c>
+      <c r="B315" s="6" t="inlineStr">
+        <is>
+          <t>https://time-keeper.com/</t>
+        </is>
+      </c>
+      <c r="C315" s="5" t="inlineStr">
+        <is>
+          <t>Ali Al-Yousifi</t>
+        </is>
+      </c>
+      <c r="D315" s="5" t="inlineStr">
+        <is>
+          <t>Owner / Co-founder</t>
+        </is>
+      </c>
+      <c r="E315" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F315" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G315" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>Aldur Almanthoor</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="inlineStr">
+        <is>
+          <t>https://www.aldurco.com/</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>Abdulaziz Alrefaie</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer, Aldur Almanthoor</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G316" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/abdulaziz-alrefaie-a2b449104</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="5" t="inlineStr">
+        <is>
+          <t>GAMESQ8.com</t>
+        </is>
+      </c>
+      <c r="B317" s="6" t="inlineStr">
+        <is>
+          <t>https://gamesq8.com/</t>
+        </is>
+      </c>
+      <c r="C317" s="5" t="inlineStr">
+        <is>
+          <t>Ammar Jassim Hussain Ashkanani</t>
+        </is>
+      </c>
+      <c r="D317" s="5" t="inlineStr">
+        <is>
+          <t>Company Manager / Owner-operator (app publisher)</t>
+        </is>
+      </c>
+      <c r="E317" s="5" t="inlineStr">
+        <is>
+          <t>+965 9559 2299</t>
+        </is>
+      </c>
+      <c r="F317" s="5" t="inlineStr">
+        <is>
+          <t>info@gamesq8.com</t>
+        </is>
+      </c>
+      <c r="G317" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>Zue</t>
+        </is>
+      </c>
+      <c r="B318" s="3" t="inlineStr">
+        <is>
+          <t>https://www.zue.com.kw/</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>Mohammad Almutawa</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer at Zue for pet</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G318" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mohammad-almutawa-a48a11b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="5" t="inlineStr">
+        <is>
           <t>aivi</t>
         </is>
       </c>
-      <c r="B231" s="6" t="inlineStr">
+      <c r="B319" s="6" t="inlineStr">
         <is>
           <t>https://en-kw.aivi.com/</t>
         </is>
       </c>
-      <c r="C231" s="5" t="inlineStr">
+      <c r="C319" s="5" t="inlineStr">
         <is>
           <t>Vivek Rajukumar</t>
         </is>
       </c>
-      <c r="D231" s="5" t="inlineStr">
+      <c r="D319" s="5" t="inlineStr">
         <is>
           <t>Chief Executive Officer, AIVI (formerly 6thStreet, Apparel Group)</t>
         </is>
       </c>
-      <c r="E231" s="5" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="F231" s="5" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="G231" s="6" t="inlineStr">
+      <c r="E319" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F319" s="5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G319" s="6" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/vivek-rajukumar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G231"/>
+  <autoFilter ref="A1:G319"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -18578,99 +21841,256 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId348"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B184" r:id="rId349"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B185" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G185" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B186" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G186" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B187" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G187" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B188" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B189" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B190" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G190" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B191" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B192" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B193" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G193" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B194" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B195" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B196" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G196" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B197" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G197" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B198" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G198" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B199" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G199" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B200" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G200" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B201" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B202" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G202" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B203" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B204" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B205" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B206" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B207" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B208" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B209" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G209" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B210" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G210" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B211" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G211" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B212" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G212" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B213" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B214" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G214" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B215" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B216" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G216" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B217" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G217" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B218" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B219" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G219" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B220" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G220" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B221" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G221" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B222" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B223" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B224" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B225" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G225" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B226" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G226" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B227" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G227" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B228" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G228" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B229" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G229" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B230" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B231" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B186" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G186" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B187" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G187" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B188" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B189" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B190" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G190" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B191" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B192" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B193" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G193" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B194" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B195" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B196" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G196" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B197" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G197" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B198" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G198" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B199" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G199" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B200" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G200" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B201" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B202" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G202" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B203" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B204" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B205" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B206" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B207" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B208" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B209" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G209" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B210" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G210" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B211" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G211" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B212" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G212" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B213" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B214" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G214" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B215" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B216" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B217" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B218" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B219" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G219" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B220" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G220" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B221" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G221" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B222" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B223" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B224" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B225" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G225" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B226" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B227" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B228" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G228" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B229" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G229" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B230" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B231" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B232" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G232" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B233" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G233" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B234" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B235" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G235" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B236" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G236" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B237" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B238" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B239" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G239" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B240" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G240" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B241" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G241" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B242" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G242" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B243" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G243" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B244" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B245" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G245" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B246" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G246" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B247" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B248" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B249" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G249" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B250" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G250" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B251" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G251" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B252" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G252" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B253" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G253" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B254" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G254" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B255" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G255" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B256" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G256" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B257" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G257" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B258" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G258" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B259" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B260" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G260" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B261" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G261" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B262" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G262" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B263" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G263" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B264" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G264" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B265" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B266" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G266" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B267" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B268" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G268" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B269" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G269" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B270" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G270" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B271" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G271" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B272" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B273" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G273" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B274" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G274" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B275" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G275" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B276" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G276" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B277" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G277" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B278" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G278" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B279" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G279" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B280" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G280" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B281" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G281" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B282" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G282" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B283" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G283" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B284" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G284" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B285" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G285" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B286" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G286" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B287" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G287" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B288" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B289" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B290" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B291" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G291" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B292" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G292" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B293" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G293" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B294" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G294" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B295" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G295" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B296" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B297" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G297" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B298" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G298" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B299" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G299" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B300" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B301" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G301" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B302" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G302" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B303" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G303" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B304" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G304" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B305" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G305" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B306" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B307" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G307" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B308" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G308" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B309" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G309" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B310" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G310" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B311" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G311" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B312" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G312" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B313" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G313" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B314" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G314" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B315" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B316" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G316" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B317" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B318" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G318" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B319" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G319" r:id="rId600"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
